--- a/artfynd/A 56566-2025 artfynd.xlsx
+++ b/artfynd/A 56566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121062024</v>
+        <v>121176195</v>
       </c>
       <c r="B2" t="n">
-        <v>97042</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>2412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Philonotis fontana</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1,5 km SO om Gravsjö, Ly lm</t>
+          <t>Gravsjön SO 1,5 km, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679590</v>
+        <v>679572</v>
       </c>
       <c r="R2" t="n">
-        <v>7152763</v>
+        <v>7152476</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>i kanten av nerskuret dike, foto men inget belägg</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,67 +754,75 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>rikkärr igenväxande</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av rikkärr i Västerbottens län 2024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128649125</v>
+        <v>133856930</v>
       </c>
       <c r="B3" t="n">
-        <v>97534</v>
+        <v>99195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SO om Gravsjö, Ly lm</t>
+          <t>Knaften, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679566</v>
+        <v>679623</v>
       </c>
       <c r="R3" t="n">
-        <v>7152712</v>
+        <v>7152789</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,22 +865,230 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121062024</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1,5 km SO om Gravsjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>679590</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7152763</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>i kanten av nerskuret dike, foto men inget belägg</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Jonas F Grahn</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128649125</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SO om Gravsjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>679566</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7152712</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Jonas F Grahn, Henrik Sporrong</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56566-2025 artfynd.xlsx
+++ b/artfynd/A 56566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Inventering av rikkärr i Västerbottens län 2024</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121176195</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856930</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062024</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,8 +1109,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128649125</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>